--- a/digital-modeling/10 Лаба/table.xlsx
+++ b/digital-modeling/10 Лаба/table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexv\OneDrive\projects\labs\digital-modeling\10 Лаба\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anna0\Documents\GitHub\university\digital-modeling\10 Лаба\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBC4F72-504A-4309-8731-702A697E3671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC76E437-9BDC-446A-8476-711371D314CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="3180" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="20">
   <si>
     <t>TS</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>333.15</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>SINGLE</t>
+  </si>
+  <si>
+    <t>POINT</t>
+  </si>
+  <si>
+    <t>ENERGY</t>
   </si>
 </sst>
 </file>
@@ -91,15 +103,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -111,7 +131,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -119,15 +139,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -408,18 +449,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:G21"/>
+  <dimension ref="B2:N24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -429,8 +471,23 @@
       <c r="G3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="5">
+        <v>-467.32387199999999</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -449,8 +506,23 @@
       <c r="G4" s="2">
         <v>-242.20643747236301</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="5">
+        <v>-467.32852339999999</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -469,8 +541,23 @@
       <c r="G5" s="2">
         <v>-242.151321225266</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="5">
+        <v>-467.33136450000001</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -487,8 +574,23 @@
         <v>5</v>
       </c>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="5">
+        <v>-467.3373393</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -507,8 +609,23 @@
       <c r="G7" s="2">
         <v>-242.18220703165301</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="5">
+        <v>-467.34654940000001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -524,133 +641,389 @@
       <c r="F8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="5">
+        <v>-467.34645899999998</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="5">
+        <v>-467.34822500000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N10" s="5">
+        <v>-467.3487902</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C11" s="2">
+        <v>6.9453174000000006E-2</v>
+      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="2">
         <v>6.9453174000000006E-2</v>
       </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="3">
-        <v>5.5284297000000003E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G11" s="3"/>
+      <c r="J11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="5">
+        <v>-467.34931779999999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2">
-        <v>6.9453174000000006E-2</v>
+        <v>182.35</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2">
+        <v>145.15</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="J12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" s="5">
+        <v>-467.3495254</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2">
+        <v>52.794901500000002</v>
+      </c>
+      <c r="E13" s="3">
         <v>5.5284297000000003E-2</v>
       </c>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2">
-        <v>182.35</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2">
-        <v>145.15</v>
-      </c>
       <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="5">
+        <v>-467.34971880000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2">
         <v>1.1184152380000001</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2">
+        <v>5.5284297000000003E-2</v>
+      </c>
       <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="2">
-        <v>52.794901500000002</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="5">
+        <v>-467.34987480000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" s="5">
+        <v>-467.34998430000002</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
       <c r="C16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N16" s="5">
+        <v>-467.35003619999998</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6.9514522999999995E-2</v>
       </c>
       <c r="E17" s="2">
         <v>6.9514522999999995E-2</v>
       </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="J17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" s="5">
+        <v>-467.3500932</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2">
+        <v>182.5</v>
+      </c>
+      <c r="E18" s="2">
+        <v>145.08000000000001</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" s="5">
+        <v>-467.35007880000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2">
+        <v>52.794901500000002</v>
+      </c>
+      <c r="E19" s="3">
         <v>5.5260272999999999E-2</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="2">
-        <v>6.9514522999999995E-2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>5.5260272999999999E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2">
-        <v>182.5</v>
-      </c>
-      <c r="E19" s="2">
-        <v>145.08000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N19" s="5">
+        <v>-467.35012219999999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2">
         <v>1.1184152380000001</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2">
-        <v>52.794901500000002</v>
+      <c r="E20" s="2">
+        <v>5.5260272999999999E-2</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N20" s="5">
+        <v>-467.3501392</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N21" s="5">
+        <v>-467.35014860000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N22" s="5">
+        <v>-467.35014990000002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N23" s="5">
+        <v>-467.3501546</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N24" s="5">
+        <v>-467.3501559</v>
       </c>
     </row>
   </sheetData>
